--- a/output/ranking.xlsx
+++ b/output/ranking.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,20 +463,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>Japão</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9293</v>
+        <v>7098</v>
       </c>
       <c r="C2" t="n">
-        <v>4289</v>
+        <v>28538</v>
       </c>
       <c r="D2" t="n">
-        <v>13582</v>
+        <v>35636</v>
       </c>
       <c r="E2" t="n">
-        <v>5004</v>
+        <v>-21440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -487,20 +487,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Espanha</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10676</v>
+        <v>9293</v>
       </c>
       <c r="C3" t="n">
-        <v>2039</v>
+        <v>4289</v>
       </c>
       <c r="D3" t="n">
-        <v>12715</v>
+        <v>13582</v>
       </c>
       <c r="E3" t="n">
-        <v>8637</v>
+        <v>5004</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -511,20 +511,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>França</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7089</v>
+        <v>10676</v>
       </c>
       <c r="C4" t="n">
-        <v>5419</v>
+        <v>2039</v>
       </c>
       <c r="D4" t="n">
-        <v>12508</v>
+        <v>12715</v>
       </c>
       <c r="E4" t="n">
-        <v>1670</v>
+        <v>8637</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -535,20 +535,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>Suíça</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6017</v>
+        <v>7089</v>
       </c>
       <c r="C5" t="n">
-        <v>3465</v>
+        <v>5419</v>
       </c>
       <c r="D5" t="n">
-        <v>9482</v>
+        <v>12508</v>
       </c>
       <c r="E5" t="n">
-        <v>2552</v>
+        <v>1670</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -559,20 +559,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>Austrália</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7194</v>
+        <v>6017</v>
       </c>
       <c r="C6" t="n">
-        <v>1776</v>
+        <v>3465</v>
       </c>
       <c r="D6" t="n">
-        <v>8970</v>
+        <v>9482</v>
       </c>
       <c r="E6" t="n">
-        <v>5418</v>
+        <v>2552</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -583,20 +583,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Holanda</t>
+          <t>Irlanda</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5578</v>
+        <v>7194</v>
       </c>
       <c r="C7" t="n">
-        <v>1383</v>
+        <v>1776</v>
       </c>
       <c r="D7" t="n">
-        <v>6961</v>
+        <v>8970</v>
       </c>
       <c r="E7" t="n">
-        <v>4195</v>
+        <v>5418</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -607,20 +607,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Holanda</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3064</v>
+        <v>5578</v>
       </c>
       <c r="C8" t="n">
-        <v>2154</v>
+        <v>1383</v>
       </c>
       <c r="D8" t="n">
-        <v>5218</v>
+        <v>6961</v>
       </c>
       <c r="E8" t="n">
-        <v>910</v>
+        <v>4195</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -631,20 +631,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2127</v>
+        <v>3064</v>
       </c>
       <c r="C9" t="n">
-        <v>591</v>
+        <v>2154</v>
       </c>
       <c r="D9" t="n">
-        <v>2718</v>
+        <v>5218</v>
       </c>
       <c r="E9" t="n">
-        <v>1536</v>
+        <v>910</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -655,20 +655,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>Líbano</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1383</v>
+        <v>2736</v>
       </c>
       <c r="C10" t="n">
-        <v>243</v>
+        <v>1276</v>
       </c>
       <c r="D10" t="n">
-        <v>1626</v>
+        <v>4012</v>
       </c>
       <c r="E10" t="n">
-        <v>1140</v>
+        <v>1460</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -679,20 +679,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>Suécia</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1178</v>
+        <v>2127</v>
       </c>
       <c r="C11" t="n">
-        <v>393</v>
+        <v>591</v>
       </c>
       <c r="D11" t="n">
-        <v>1571</v>
+        <v>2718</v>
       </c>
       <c r="E11" t="n">
-        <v>785</v>
+        <v>1536</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -703,20 +703,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Emirados Árabes</t>
+          <t>Dinamarca</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>643</v>
+        <v>1383</v>
       </c>
       <c r="C12" t="n">
-        <v>772</v>
+        <v>243</v>
       </c>
       <c r="D12" t="n">
-        <v>1415</v>
+        <v>1626</v>
       </c>
       <c r="E12" t="n">
-        <v>-129</v>
+        <v>1140</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -727,20 +727,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Áustria</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>820</v>
+        <v>1178</v>
       </c>
       <c r="C13" t="n">
-        <v>248</v>
+        <v>393</v>
       </c>
       <c r="D13" t="n">
-        <v>1068</v>
+        <v>1571</v>
       </c>
       <c r="E13" t="n">
-        <v>572</v>
+        <v>785</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -751,20 +751,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jordânia</t>
+          <t>Emirados Árabes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>725</v>
+        <v>643</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>772</v>
       </c>
       <c r="D14" t="n">
-        <v>801</v>
+        <v>1415</v>
       </c>
       <c r="E14" t="n">
-        <v>649</v>
+        <v>-129</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -775,20 +775,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>502</v>
+        <v>820</v>
       </c>
       <c r="C15" t="n">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="D15" t="n">
-        <v>769</v>
+        <v>1068</v>
       </c>
       <c r="E15" t="n">
-        <v>235</v>
+        <v>572</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -799,20 +799,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>Palestina</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="C16" t="n">
-        <v>185</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>735</v>
+        <v>1046</v>
       </c>
       <c r="E16" t="n">
-        <v>365</v>
+        <v>954</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -823,20 +823,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>550</v>
+        <v>166</v>
       </c>
       <c r="C17" t="n">
-        <v>185</v>
+        <v>699</v>
       </c>
       <c r="D17" t="n">
-        <v>735</v>
+        <v>865</v>
       </c>
       <c r="E17" t="n">
-        <v>365</v>
+        <v>-533</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -847,20 +847,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nova Zelândia</t>
+          <t>Jordânia</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>418</v>
+        <v>725</v>
       </c>
       <c r="C18" t="n">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="D18" t="n">
-        <v>519</v>
+        <v>801</v>
       </c>
       <c r="E18" t="n">
-        <v>317</v>
+        <v>649</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -871,20 +871,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>355</v>
+        <v>502</v>
       </c>
       <c r="C19" t="n">
-        <v>117</v>
+        <v>267</v>
       </c>
       <c r="D19" t="n">
-        <v>472</v>
+        <v>769</v>
       </c>
       <c r="E19" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -895,20 +895,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>África do Sul</t>
+          <t>Finlândia</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>186</v>
+        <v>550</v>
       </c>
       <c r="C20" t="n">
-        <v>256</v>
+        <v>185</v>
       </c>
       <c r="D20" t="n">
-        <v>442</v>
+        <v>735</v>
       </c>
       <c r="E20" t="n">
-        <v>-70</v>
+        <v>365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -919,20 +919,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>Estônia</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>304</v>
+        <v>550</v>
       </c>
       <c r="C21" t="n">
-        <v>86</v>
+        <v>185</v>
       </c>
       <c r="D21" t="n">
-        <v>390</v>
+        <v>735</v>
       </c>
       <c r="E21" t="n">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -943,20 +943,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>Grécia</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="C22" t="n">
-        <v>89</v>
+        <v>311</v>
       </c>
       <c r="D22" t="n">
-        <v>357</v>
+        <v>566</v>
       </c>
       <c r="E22" t="n">
-        <v>179</v>
+        <v>-56</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -967,20 +967,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Catar</t>
+          <t>Nova Zelândia</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>159</v>
+        <v>418</v>
       </c>
       <c r="C23" t="n">
-        <v>195</v>
+        <v>101</v>
       </c>
       <c r="D23" t="n">
-        <v>354</v>
+        <v>519</v>
       </c>
       <c r="E23" t="n">
-        <v>-36</v>
+        <v>317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -991,20 +991,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Hungria</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>167</v>
+        <v>355</v>
       </c>
       <c r="C24" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D24" t="n">
-        <v>285</v>
+        <v>472</v>
       </c>
       <c r="E24" t="n">
-        <v>49</v>
+        <v>238</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1015,20 +1015,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>África do Sul</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="C25" t="n">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="D25" t="n">
-        <v>230</v>
+        <v>442</v>
       </c>
       <c r="E25" t="n">
-        <v>66</v>
+        <v>-70</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1039,20 +1039,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Moçambique</t>
+          <t>República Tcheca</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>108</v>
+        <v>304</v>
       </c>
       <c r="C26" t="n">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="D26" t="n">
-        <v>225</v>
+        <v>390</v>
       </c>
       <c r="E26" t="n">
-        <v>-9</v>
+        <v>218</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1063,20 +1063,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>Polônia</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>67</v>
+        <v>268</v>
       </c>
       <c r="C27" t="n">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="D27" t="n">
-        <v>95</v>
+        <v>357</v>
       </c>
       <c r="E27" t="n">
-        <v>39</v>
+        <v>179</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1087,20 +1087,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Catar</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>59</v>
+        <v>159</v>
       </c>
       <c r="C28" t="n">
-        <v>22</v>
+        <v>195</v>
       </c>
       <c r="D28" t="n">
-        <v>81</v>
+        <v>354</v>
       </c>
       <c r="E28" t="n">
-        <v>37</v>
+        <v>-36</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1111,20 +1111,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Arábia Saudita</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>49</v>
+        <v>213</v>
       </c>
       <c r="C29" t="n">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="D29" t="n">
-        <v>80</v>
+        <v>334</v>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1135,20 +1135,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Filipinas</t>
+          <t>Síria</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="C30" t="n">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="D30" t="n">
-        <v>66</v>
+        <v>334</v>
       </c>
       <c r="E30" t="n">
-        <v>-12</v>
+        <v>92</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1159,20 +1159,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>40</v>
+        <v>167</v>
       </c>
       <c r="C31" t="n">
-        <v>25</v>
+        <v>118</v>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>285</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1183,20 +1183,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>Coreia do Sul</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="C32" t="n">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>230</v>
       </c>
       <c r="E32" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1207,20 +1207,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>Moçambique</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="C33" t="n">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="D33" t="n">
-        <v>57</v>
+        <v>225</v>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>-9</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1231,20 +1231,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sérvia</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="C34" t="n">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="D34" t="n">
-        <v>48</v>
+        <v>224</v>
       </c>
       <c r="E34" t="n">
-        <v>22</v>
+        <v>-36</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1255,20 +1255,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Quênia</t>
+          <t>Tailândia</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C35" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D35" t="n">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="E35" t="n">
-        <v>13</v>
+        <v>-4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1279,20 +1279,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>Eslovênia</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="C36" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D36" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="E36" t="n">
-        <v>-8</v>
+        <v>39</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1303,22 +1303,310 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Malásia</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>41</v>
+      </c>
+      <c r="C37" t="n">
+        <v>44</v>
+      </c>
+      <c r="D37" t="n">
+        <v>85</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>59</v>
+      </c>
+      <c r="C38" t="n">
+        <v>22</v>
+      </c>
+      <c r="D38" t="n">
+        <v>81</v>
+      </c>
+      <c r="E38" t="n">
+        <v>37</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Arábia Saudita</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>49</v>
+      </c>
+      <c r="C39" t="n">
+        <v>31</v>
+      </c>
+      <c r="D39" t="n">
+        <v>80</v>
+      </c>
+      <c r="E39" t="n">
+        <v>18</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>62</v>
+      </c>
+      <c r="C40" t="n">
+        <v>17</v>
+      </c>
+      <c r="D40" t="n">
+        <v>79</v>
+      </c>
+      <c r="E40" t="n">
+        <v>45</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Filipinas</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>27</v>
+      </c>
+      <c r="C41" t="n">
+        <v>39</v>
+      </c>
+      <c r="D41" t="n">
+        <v>66</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Romênia</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>40</v>
+      </c>
+      <c r="C42" t="n">
+        <v>25</v>
+      </c>
+      <c r="D42" t="n">
+        <v>65</v>
+      </c>
+      <c r="E42" t="n">
+        <v>15</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Eslováquia</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>47</v>
+      </c>
+      <c r="C43" t="n">
+        <v>14</v>
+      </c>
+      <c r="D43" t="n">
+        <v>61</v>
+      </c>
+      <c r="E43" t="n">
+        <v>33</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Croácia</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>31</v>
+      </c>
+      <c r="C44" t="n">
+        <v>26</v>
+      </c>
+      <c r="D44" t="n">
+        <v>57</v>
+      </c>
+      <c r="E44" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chipre</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>29</v>
+      </c>
+      <c r="C45" t="n">
+        <v>25</v>
+      </c>
+      <c r="D45" t="n">
+        <v>54</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sérvia</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>35</v>
+      </c>
+      <c r="C46" t="n">
+        <v>13</v>
+      </c>
+      <c r="D46" t="n">
+        <v>48</v>
+      </c>
+      <c r="E46" t="n">
+        <v>22</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Quênia</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>29</v>
+      </c>
+      <c r="C47" t="n">
+        <v>16</v>
+      </c>
+      <c r="D47" t="n">
+        <v>45</v>
+      </c>
+      <c r="E47" t="n">
+        <v>13</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Indonésia</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>15</v>
+      </c>
+      <c r="C48" t="n">
+        <v>23</v>
+      </c>
+      <c r="D48" t="n">
+        <v>38</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>Marrocos</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B49" t="n">
         <v>31</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C49" t="n">
         <v>6</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D49" t="n">
         <v>37</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E49" t="n">
         <v>25</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
         </is>

--- a/output/ranking.xlsx
+++ b/output/ranking.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,20 +487,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>Alemanha</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9293</v>
+        <v>16549</v>
       </c>
       <c r="C3" t="n">
-        <v>4289</v>
+        <v>4374</v>
       </c>
       <c r="D3" t="n">
-        <v>13582</v>
+        <v>20923</v>
       </c>
       <c r="E3" t="n">
-        <v>5004</v>
+        <v>12175</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -511,20 +511,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Espanha</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10676</v>
+        <v>9293</v>
       </c>
       <c r="C4" t="n">
-        <v>2039</v>
+        <v>4289</v>
       </c>
       <c r="D4" t="n">
-        <v>12715</v>
+        <v>13582</v>
       </c>
       <c r="E4" t="n">
-        <v>8637</v>
+        <v>5004</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -535,20 +535,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>Itália</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7089</v>
+        <v>7921</v>
       </c>
       <c r="C5" t="n">
-        <v>5419</v>
+        <v>5283</v>
       </c>
       <c r="D5" t="n">
-        <v>12508</v>
+        <v>13204</v>
       </c>
       <c r="E5" t="n">
-        <v>1670</v>
+        <v>2638</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -559,20 +559,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>França</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6017</v>
+        <v>10676</v>
       </c>
       <c r="C6" t="n">
-        <v>3465</v>
+        <v>2039</v>
       </c>
       <c r="D6" t="n">
-        <v>9482</v>
+        <v>12715</v>
       </c>
       <c r="E6" t="n">
-        <v>2552</v>
+        <v>8637</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -583,20 +583,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>Suíça</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7194</v>
+        <v>7089</v>
       </c>
       <c r="C7" t="n">
-        <v>1776</v>
+        <v>5419</v>
       </c>
       <c r="D7" t="n">
-        <v>8970</v>
+        <v>12508</v>
       </c>
       <c r="E7" t="n">
-        <v>5418</v>
+        <v>1670</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -607,20 +607,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Holanda</t>
+          <t>Austrália</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5578</v>
+        <v>6017</v>
       </c>
       <c r="C8" t="n">
-        <v>1383</v>
+        <v>3465</v>
       </c>
       <c r="D8" t="n">
-        <v>6961</v>
+        <v>9482</v>
       </c>
       <c r="E8" t="n">
-        <v>4195</v>
+        <v>2552</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -631,20 +631,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Irlanda</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3064</v>
+        <v>7194</v>
       </c>
       <c r="C9" t="n">
-        <v>2154</v>
+        <v>1776</v>
       </c>
       <c r="D9" t="n">
-        <v>5218</v>
+        <v>8970</v>
       </c>
       <c r="E9" t="n">
-        <v>910</v>
+        <v>5418</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -655,20 +655,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Líbano</t>
+          <t>Holanda</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2736</v>
+        <v>5578</v>
       </c>
       <c r="C10" t="n">
-        <v>1276</v>
+        <v>1383</v>
       </c>
       <c r="D10" t="n">
-        <v>4012</v>
+        <v>6961</v>
       </c>
       <c r="E10" t="n">
-        <v>1460</v>
+        <v>4195</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -679,20 +679,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2127</v>
+        <v>3064</v>
       </c>
       <c r="C11" t="n">
-        <v>591</v>
+        <v>2154</v>
       </c>
       <c r="D11" t="n">
-        <v>2718</v>
+        <v>5218</v>
       </c>
       <c r="E11" t="n">
-        <v>1536</v>
+        <v>910</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -703,20 +703,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>Líbano</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1383</v>
+        <v>2736</v>
       </c>
       <c r="C12" t="n">
-        <v>243</v>
+        <v>1276</v>
       </c>
       <c r="D12" t="n">
-        <v>1626</v>
+        <v>4012</v>
       </c>
       <c r="E12" t="n">
-        <v>1140</v>
+        <v>1460</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -727,20 +727,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>Suécia</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1178</v>
+        <v>2127</v>
       </c>
       <c r="C13" t="n">
-        <v>393</v>
+        <v>591</v>
       </c>
       <c r="D13" t="n">
-        <v>1571</v>
+        <v>2718</v>
       </c>
       <c r="E13" t="n">
-        <v>785</v>
+        <v>1536</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -751,20 +751,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Emirados Árabes</t>
+          <t>Dinamarca</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>643</v>
+        <v>1383</v>
       </c>
       <c r="C14" t="n">
-        <v>772</v>
+        <v>243</v>
       </c>
       <c r="D14" t="n">
-        <v>1415</v>
+        <v>1626</v>
       </c>
       <c r="E14" t="n">
-        <v>-129</v>
+        <v>1140</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -775,20 +775,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Áustria</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>820</v>
+        <v>1178</v>
       </c>
       <c r="C15" t="n">
-        <v>248</v>
+        <v>393</v>
       </c>
       <c r="D15" t="n">
-        <v>1068</v>
+        <v>1571</v>
       </c>
       <c r="E15" t="n">
-        <v>572</v>
+        <v>785</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -799,20 +799,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Palestina</t>
+          <t>Emirados Árabes</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1000</v>
+        <v>643</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>772</v>
       </c>
       <c r="D16" t="n">
-        <v>1046</v>
+        <v>1415</v>
       </c>
       <c r="E16" t="n">
-        <v>954</v>
+        <v>-129</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -823,20 +823,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>166</v>
+        <v>820</v>
       </c>
       <c r="C17" t="n">
-        <v>699</v>
+        <v>248</v>
       </c>
       <c r="D17" t="n">
-        <v>865</v>
+        <v>1068</v>
       </c>
       <c r="E17" t="n">
-        <v>-533</v>
+        <v>572</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -847,20 +847,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jordânia</t>
+          <t>Palestina</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>725</v>
+        <v>1000</v>
       </c>
       <c r="C18" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="D18" t="n">
-        <v>801</v>
+        <v>1046</v>
       </c>
       <c r="E18" t="n">
-        <v>649</v>
+        <v>954</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -871,20 +871,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>502</v>
+        <v>166</v>
       </c>
       <c r="C19" t="n">
-        <v>267</v>
+        <v>699</v>
       </c>
       <c r="D19" t="n">
-        <v>769</v>
+        <v>865</v>
       </c>
       <c r="E19" t="n">
-        <v>235</v>
+        <v>-533</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -895,20 +895,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>Jordânia</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>550</v>
+        <v>725</v>
       </c>
       <c r="C20" t="n">
-        <v>185</v>
+        <v>76</v>
       </c>
       <c r="D20" t="n">
-        <v>735</v>
+        <v>801</v>
       </c>
       <c r="E20" t="n">
-        <v>365</v>
+        <v>649</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -919,20 +919,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>550</v>
+        <v>502</v>
       </c>
       <c r="C21" t="n">
-        <v>185</v>
+        <v>267</v>
       </c>
       <c r="D21" t="n">
-        <v>735</v>
+        <v>769</v>
       </c>
       <c r="E21" t="n">
-        <v>365</v>
+        <v>235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -943,20 +943,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>Finlândia</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>255</v>
+        <v>550</v>
       </c>
       <c r="C22" t="n">
-        <v>311</v>
+        <v>185</v>
       </c>
       <c r="D22" t="n">
-        <v>566</v>
+        <v>735</v>
       </c>
       <c r="E22" t="n">
-        <v>-56</v>
+        <v>365</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -967,20 +967,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nova Zelândia</t>
+          <t>Estônia</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>418</v>
+        <v>550</v>
       </c>
       <c r="C23" t="n">
-        <v>101</v>
+        <v>185</v>
       </c>
       <c r="D23" t="n">
-        <v>519</v>
+        <v>735</v>
       </c>
       <c r="E23" t="n">
-        <v>317</v>
+        <v>365</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -991,20 +991,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>Grécia</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>355</v>
+        <v>255</v>
       </c>
       <c r="C24" t="n">
-        <v>117</v>
+        <v>311</v>
       </c>
       <c r="D24" t="n">
-        <v>472</v>
+        <v>566</v>
       </c>
       <c r="E24" t="n">
-        <v>238</v>
+        <v>-56</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1015,20 +1015,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>África do Sul</t>
+          <t>Nova Zelândia</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>186</v>
+        <v>418</v>
       </c>
       <c r="C25" t="n">
-        <v>256</v>
+        <v>101</v>
       </c>
       <c r="D25" t="n">
-        <v>442</v>
+        <v>519</v>
       </c>
       <c r="E25" t="n">
-        <v>-70</v>
+        <v>317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1039,20 +1039,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>Hungria</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>304</v>
+        <v>355</v>
       </c>
       <c r="C26" t="n">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="D26" t="n">
-        <v>390</v>
+        <v>472</v>
       </c>
       <c r="E26" t="n">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1063,20 +1063,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>África do Sul</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>268</v>
+        <v>186</v>
       </c>
       <c r="C27" t="n">
-        <v>89</v>
+        <v>256</v>
       </c>
       <c r="D27" t="n">
-        <v>357</v>
+        <v>442</v>
       </c>
       <c r="E27" t="n">
-        <v>179</v>
+        <v>-70</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1087,20 +1087,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Catar</t>
+          <t>República Tcheca</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>159</v>
+        <v>304</v>
       </c>
       <c r="C28" t="n">
-        <v>195</v>
+        <v>86</v>
       </c>
       <c r="D28" t="n">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E28" t="n">
-        <v>-36</v>
+        <v>218</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1111,20 +1111,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Polônia</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>213</v>
+        <v>268</v>
       </c>
       <c r="C29" t="n">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="D29" t="n">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="E29" t="n">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1135,20 +1135,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Síria</t>
+          <t>Catar</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>213</v>
+        <v>159</v>
       </c>
       <c r="C30" t="n">
-        <v>121</v>
+        <v>195</v>
       </c>
       <c r="D30" t="n">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="E30" t="n">
-        <v>92</v>
+        <v>-36</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1159,20 +1159,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Síria</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>167</v>
+        <v>213</v>
       </c>
       <c r="C31" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D31" t="n">
-        <v>285</v>
+        <v>334</v>
       </c>
       <c r="E31" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1183,20 +1183,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>148</v>
+        <v>213</v>
       </c>
       <c r="C32" t="n">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="D32" t="n">
-        <v>230</v>
+        <v>334</v>
       </c>
       <c r="E32" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1207,20 +1207,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Moçambique</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="C33" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D33" t="n">
-        <v>225</v>
+        <v>285</v>
       </c>
       <c r="E33" t="n">
-        <v>-9</v>
+        <v>49</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1231,20 +1231,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Coreia do Sul</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="C34" t="n">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="D34" t="n">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E34" t="n">
-        <v>-36</v>
+        <v>66</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1255,20 +1255,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tailândia</t>
+          <t>Moçambique</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="C35" t="n">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="D35" t="n">
-        <v>116</v>
+        <v>225</v>
       </c>
       <c r="E35" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1279,20 +1279,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="C36" t="n">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="D36" t="n">
-        <v>95</v>
+        <v>224</v>
       </c>
       <c r="E36" t="n">
-        <v>39</v>
+        <v>-36</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1303,20 +1303,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Malásia</t>
+          <t>Tailândia</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C37" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D37" t="n">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="E37" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1327,20 +1327,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Eslovênia</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C38" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D38" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E38" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1351,20 +1351,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Arábia Saudita</t>
+          <t>Malásia</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C39" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D39" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E39" t="n">
-        <v>18</v>
+        <v>-3</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1375,20 +1375,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C40" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D40" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E40" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1399,20 +1399,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Filipinas</t>
+          <t>Arábia Saudita</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C41" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D41" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E41" t="n">
-        <v>-12</v>
+        <v>18</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1423,20 +1423,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C42" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D42" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E42" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1447,20 +1447,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C43" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D43" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E43" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1471,20 +1471,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>Filipinas</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C44" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D44" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>-12</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1495,20 +1495,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>Romênia</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C45" t="n">
         <v>25</v>
       </c>
       <c r="D45" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1519,20 +1519,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sérvia</t>
+          <t>Eslováquia</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D46" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E46" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1543,20 +1543,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Quênia</t>
+          <t>Croácia</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C47" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D47" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1567,20 +1567,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>Chipre</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C48" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D48" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="E48" t="n">
-        <v>-8</v>
+        <v>4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1591,22 +1591,94 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>Sérvia</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>35</v>
+      </c>
+      <c r="C49" t="n">
+        <v>13</v>
+      </c>
+      <c r="D49" t="n">
+        <v>48</v>
+      </c>
+      <c r="E49" t="n">
+        <v>22</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Quênia</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>29</v>
+      </c>
+      <c r="C50" t="n">
+        <v>16</v>
+      </c>
+      <c r="D50" t="n">
+        <v>45</v>
+      </c>
+      <c r="E50" t="n">
+        <v>13</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Indonésia</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>15</v>
+      </c>
+      <c r="C51" t="n">
+        <v>23</v>
+      </c>
+      <c r="D51" t="n">
+        <v>38</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Marrocos</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B52" t="n">
         <v>31</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C52" t="n">
         <v>6</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D52" t="n">
         <v>37</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E52" t="n">
         <v>25</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
         </is>

--- a/output/ranking.xlsx
+++ b/output/ranking.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,20 +463,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7098</v>
+        <v>34319</v>
       </c>
       <c r="C2" t="n">
-        <v>28538</v>
+        <v>23433</v>
       </c>
       <c r="D2" t="n">
-        <v>35636</v>
+        <v>57752</v>
       </c>
       <c r="E2" t="n">
-        <v>-21440</v>
+        <v>10886</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -487,20 +487,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>Japão</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16549</v>
+        <v>7098</v>
       </c>
       <c r="C3" t="n">
-        <v>4374</v>
+        <v>28538</v>
       </c>
       <c r="D3" t="n">
-        <v>20923</v>
+        <v>35636</v>
       </c>
       <c r="E3" t="n">
-        <v>12175</v>
+        <v>-21440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -511,20 +511,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>Alemanha</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9293</v>
+        <v>16549</v>
       </c>
       <c r="C4" t="n">
-        <v>4289</v>
+        <v>4374</v>
       </c>
       <c r="D4" t="n">
-        <v>13582</v>
+        <v>20923</v>
       </c>
       <c r="E4" t="n">
-        <v>5004</v>
+        <v>12175</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -535,20 +535,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7921</v>
+        <v>10968</v>
       </c>
       <c r="C5" t="n">
-        <v>5283</v>
+        <v>6349</v>
       </c>
       <c r="D5" t="n">
-        <v>13204</v>
+        <v>17317</v>
       </c>
       <c r="E5" t="n">
-        <v>2638</v>
+        <v>4619</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -559,20 +559,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Espanha</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10676</v>
+        <v>9293</v>
       </c>
       <c r="C6" t="n">
-        <v>2039</v>
+        <v>4289</v>
       </c>
       <c r="D6" t="n">
-        <v>12715</v>
+        <v>13582</v>
       </c>
       <c r="E6" t="n">
-        <v>8637</v>
+        <v>5004</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -583,20 +583,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>Itália</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7089</v>
+        <v>7921</v>
       </c>
       <c r="C7" t="n">
-        <v>5419</v>
+        <v>5283</v>
       </c>
       <c r="D7" t="n">
-        <v>12508</v>
+        <v>13204</v>
       </c>
       <c r="E7" t="n">
-        <v>1670</v>
+        <v>2638</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -607,20 +607,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>França</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6017</v>
+        <v>10676</v>
       </c>
       <c r="C8" t="n">
-        <v>3465</v>
+        <v>2039</v>
       </c>
       <c r="D8" t="n">
-        <v>9482</v>
+        <v>12715</v>
       </c>
       <c r="E8" t="n">
-        <v>2552</v>
+        <v>8637</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -631,20 +631,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>Suíça</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7194</v>
+        <v>7089</v>
       </c>
       <c r="C9" t="n">
-        <v>1776</v>
+        <v>5419</v>
       </c>
       <c r="D9" t="n">
-        <v>8970</v>
+        <v>12508</v>
       </c>
       <c r="E9" t="n">
-        <v>5418</v>
+        <v>1670</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -655,20 +655,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Holanda</t>
+          <t>Austrália</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5578</v>
+        <v>6017</v>
       </c>
       <c r="C10" t="n">
-        <v>1383</v>
+        <v>3465</v>
       </c>
       <c r="D10" t="n">
-        <v>6961</v>
+        <v>9482</v>
       </c>
       <c r="E10" t="n">
-        <v>4195</v>
+        <v>2552</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -679,20 +679,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Irlanda</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3064</v>
+        <v>7194</v>
       </c>
       <c r="C11" t="n">
-        <v>2154</v>
+        <v>1776</v>
       </c>
       <c r="D11" t="n">
-        <v>5218</v>
+        <v>8970</v>
       </c>
       <c r="E11" t="n">
-        <v>910</v>
+        <v>5418</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -703,20 +703,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Líbano</t>
+          <t>Holanda</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2736</v>
+        <v>5578</v>
       </c>
       <c r="C12" t="n">
-        <v>1276</v>
+        <v>1383</v>
       </c>
       <c r="D12" t="n">
-        <v>4012</v>
+        <v>6961</v>
       </c>
       <c r="E12" t="n">
-        <v>1460</v>
+        <v>4195</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -727,20 +727,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2127</v>
+        <v>3064</v>
       </c>
       <c r="C13" t="n">
-        <v>591</v>
+        <v>2154</v>
       </c>
       <c r="D13" t="n">
-        <v>2718</v>
+        <v>5218</v>
       </c>
       <c r="E13" t="n">
-        <v>1536</v>
+        <v>910</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -751,20 +751,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>Líbano</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1383</v>
+        <v>2736</v>
       </c>
       <c r="C14" t="n">
-        <v>243</v>
+        <v>1276</v>
       </c>
       <c r="D14" t="n">
-        <v>1626</v>
+        <v>4012</v>
       </c>
       <c r="E14" t="n">
-        <v>1140</v>
+        <v>1460</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -775,20 +775,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>Suécia</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1178</v>
+        <v>2127</v>
       </c>
       <c r="C15" t="n">
-        <v>393</v>
+        <v>591</v>
       </c>
       <c r="D15" t="n">
-        <v>1571</v>
+        <v>2718</v>
       </c>
       <c r="E15" t="n">
-        <v>785</v>
+        <v>1536</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -799,20 +799,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Emirados Árabes</t>
+          <t>Dinamarca</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>643</v>
+        <v>1383</v>
       </c>
       <c r="C16" t="n">
-        <v>772</v>
+        <v>243</v>
       </c>
       <c r="D16" t="n">
-        <v>1415</v>
+        <v>1626</v>
       </c>
       <c r="E16" t="n">
-        <v>-129</v>
+        <v>1140</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -823,20 +823,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Áustria</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>820</v>
+        <v>1178</v>
       </c>
       <c r="C17" t="n">
-        <v>248</v>
+        <v>393</v>
       </c>
       <c r="D17" t="n">
-        <v>1068</v>
+        <v>1571</v>
       </c>
       <c r="E17" t="n">
-        <v>572</v>
+        <v>785</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -847,20 +847,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Palestina</t>
+          <t>Emirados Árabes</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1000</v>
+        <v>643</v>
       </c>
       <c r="C18" t="n">
-        <v>46</v>
+        <v>772</v>
       </c>
       <c r="D18" t="n">
-        <v>1046</v>
+        <v>1415</v>
       </c>
       <c r="E18" t="n">
-        <v>954</v>
+        <v>-129</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -871,20 +871,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>166</v>
+        <v>820</v>
       </c>
       <c r="C19" t="n">
-        <v>699</v>
+        <v>248</v>
       </c>
       <c r="D19" t="n">
-        <v>865</v>
+        <v>1068</v>
       </c>
       <c r="E19" t="n">
-        <v>-533</v>
+        <v>572</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -895,20 +895,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jordânia</t>
+          <t>Palestina</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>725</v>
+        <v>1000</v>
       </c>
       <c r="C20" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>801</v>
+        <v>1046</v>
       </c>
       <c r="E20" t="n">
-        <v>649</v>
+        <v>954</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -919,20 +919,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>502</v>
+        <v>166</v>
       </c>
       <c r="C21" t="n">
-        <v>267</v>
+        <v>699</v>
       </c>
       <c r="D21" t="n">
-        <v>769</v>
+        <v>865</v>
       </c>
       <c r="E21" t="n">
-        <v>235</v>
+        <v>-533</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -943,20 +943,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>Jordânia</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>550</v>
+        <v>725</v>
       </c>
       <c r="C22" t="n">
-        <v>185</v>
+        <v>76</v>
       </c>
       <c r="D22" t="n">
-        <v>735</v>
+        <v>801</v>
       </c>
       <c r="E22" t="n">
-        <v>365</v>
+        <v>649</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -967,20 +967,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>550</v>
+        <v>502</v>
       </c>
       <c r="C23" t="n">
-        <v>185</v>
+        <v>267</v>
       </c>
       <c r="D23" t="n">
-        <v>735</v>
+        <v>769</v>
       </c>
       <c r="E23" t="n">
-        <v>365</v>
+        <v>235</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -991,20 +991,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>Finlândia</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>255</v>
+        <v>550</v>
       </c>
       <c r="C24" t="n">
-        <v>311</v>
+        <v>185</v>
       </c>
       <c r="D24" t="n">
-        <v>566</v>
+        <v>735</v>
       </c>
       <c r="E24" t="n">
-        <v>-56</v>
+        <v>365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1015,20 +1015,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nova Zelândia</t>
+          <t>Grécia</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>418</v>
+        <v>255</v>
       </c>
       <c r="C25" t="n">
-        <v>101</v>
+        <v>311</v>
       </c>
       <c r="D25" t="n">
-        <v>519</v>
+        <v>566</v>
       </c>
       <c r="E25" t="n">
-        <v>317</v>
+        <v>-56</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1039,20 +1039,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>Nova Zelândia</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>355</v>
+        <v>418</v>
       </c>
       <c r="C26" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="D26" t="n">
-        <v>472</v>
+        <v>519</v>
       </c>
       <c r="E26" t="n">
-        <v>238</v>
+        <v>317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1063,20 +1063,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>África do Sul</t>
+          <t>Hungria</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>186</v>
+        <v>355</v>
       </c>
       <c r="C27" t="n">
-        <v>256</v>
+        <v>117</v>
       </c>
       <c r="D27" t="n">
-        <v>442</v>
+        <v>472</v>
       </c>
       <c r="E27" t="n">
-        <v>-70</v>
+        <v>238</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1087,20 +1087,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>África do Sul</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>304</v>
+        <v>186</v>
       </c>
       <c r="C28" t="n">
-        <v>86</v>
+        <v>256</v>
       </c>
       <c r="D28" t="n">
-        <v>390</v>
+        <v>442</v>
       </c>
       <c r="E28" t="n">
-        <v>218</v>
+        <v>-70</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1111,20 +1111,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>República Tcheca</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>268</v>
+        <v>304</v>
       </c>
       <c r="C29" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D29" t="n">
-        <v>357</v>
+        <v>390</v>
       </c>
       <c r="E29" t="n">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1135,20 +1135,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Catar</t>
+          <t>Polônia</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>159</v>
+        <v>268</v>
       </c>
       <c r="C30" t="n">
-        <v>195</v>
+        <v>89</v>
       </c>
       <c r="D30" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E30" t="n">
-        <v>-36</v>
+        <v>179</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1159,20 +1159,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Síria</t>
+          <t>Catar</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>213</v>
+        <v>159</v>
       </c>
       <c r="C31" t="n">
-        <v>121</v>
+        <v>195</v>
       </c>
       <c r="D31" t="n">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="E31" t="n">
-        <v>92</v>
+        <v>-36</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1303,20 +1303,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tailândia</t>
+          <t>Estônia</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="C37" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="D37" t="n">
-        <v>116</v>
+        <v>193</v>
       </c>
       <c r="E37" t="n">
-        <v>-4</v>
+        <v>127</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1327,20 +1327,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>Síria</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="C38" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D38" t="n">
+        <v>117</v>
+      </c>
+      <c r="E38" t="n">
         <v>95</v>
-      </c>
-      <c r="E38" t="n">
-        <v>39</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1351,20 +1351,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Malásia</t>
+          <t>Tailândia</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C39" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D39" t="n">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="E39" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1375,20 +1375,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Eslovênia</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C40" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D40" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E40" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1399,20 +1399,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Arábia Saudita</t>
+          <t>Malásia</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C41" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D41" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E41" t="n">
-        <v>18</v>
+        <v>-3</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1423,20 +1423,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C42" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D42" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E42" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1447,20 +1447,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Arábia Saudita</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C43" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D43" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E43" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1471,20 +1471,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Filipinas</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="C44" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D44" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E44" t="n">
-        <v>-12</v>
+        <v>45</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1495,20 +1495,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C45" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D45" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E45" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1519,20 +1519,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>Egito</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C46" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D46" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E46" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1543,20 +1543,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>Filipinas</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C47" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D47" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E47" t="n">
-        <v>5</v>
+        <v>-12</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1567,20 +1567,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>Romênia</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C48" t="n">
         <v>25</v>
       </c>
       <c r="D48" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1591,20 +1591,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sérvia</t>
+          <t>Eslováquia</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D49" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1615,20 +1615,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Quênia</t>
+          <t>Croácia</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C50" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D50" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E50" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1639,20 +1639,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>Chipre</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C51" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D51" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="E51" t="n">
-        <v>-8</v>
+        <v>4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1663,22 +1663,94 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Sérvia</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>35</v>
+      </c>
+      <c r="C52" t="n">
+        <v>13</v>
+      </c>
+      <c r="D52" t="n">
+        <v>48</v>
+      </c>
+      <c r="E52" t="n">
+        <v>22</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Quênia</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>29</v>
+      </c>
+      <c r="C53" t="n">
+        <v>16</v>
+      </c>
+      <c r="D53" t="n">
+        <v>45</v>
+      </c>
+      <c r="E53" t="n">
+        <v>13</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Indonésia</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>15</v>
+      </c>
+      <c r="C54" t="n">
+        <v>23</v>
+      </c>
+      <c r="D54" t="n">
+        <v>38</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Marrocos</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B55" t="n">
         <v>31</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C55" t="n">
         <v>6</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D55" t="n">
         <v>37</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E55" t="n">
         <v>25</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
         </is>

--- a/output/ranking.xlsx
+++ b/output/ranking.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,20 +463,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34319</v>
+        <v>32023</v>
       </c>
       <c r="C2" t="n">
-        <v>23433</v>
+        <v>53718</v>
       </c>
       <c r="D2" t="n">
-        <v>57752</v>
+        <v>85741</v>
       </c>
       <c r="E2" t="n">
-        <v>10886</v>
+        <v>-21695</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -487,20 +487,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7098</v>
+        <v>34319</v>
       </c>
       <c r="C3" t="n">
-        <v>28538</v>
+        <v>23433</v>
       </c>
       <c r="D3" t="n">
-        <v>35636</v>
+        <v>57752</v>
       </c>
       <c r="E3" t="n">
-        <v>-21440</v>
+        <v>10886</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -511,20 +511,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>Japão</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16549</v>
+        <v>7098</v>
       </c>
       <c r="C4" t="n">
-        <v>4374</v>
+        <v>28538</v>
       </c>
       <c r="D4" t="n">
-        <v>20923</v>
+        <v>35636</v>
       </c>
       <c r="E4" t="n">
-        <v>12175</v>
+        <v>-21440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -535,20 +535,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10968</v>
+        <v>15776</v>
       </c>
       <c r="C5" t="n">
-        <v>6349</v>
+        <v>8501</v>
       </c>
       <c r="D5" t="n">
-        <v>17317</v>
+        <v>24277</v>
       </c>
       <c r="E5" t="n">
-        <v>4619</v>
+        <v>7275</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -559,20 +559,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>Alemanha</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9293</v>
+        <v>16549</v>
       </c>
       <c r="C6" t="n">
-        <v>4289</v>
+        <v>4374</v>
       </c>
       <c r="D6" t="n">
-        <v>13582</v>
+        <v>20923</v>
       </c>
       <c r="E6" t="n">
-        <v>5004</v>
+        <v>12175</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -583,20 +583,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7921</v>
+        <v>10968</v>
       </c>
       <c r="C7" t="n">
-        <v>5283</v>
+        <v>6349</v>
       </c>
       <c r="D7" t="n">
-        <v>13204</v>
+        <v>17317</v>
       </c>
       <c r="E7" t="n">
-        <v>2638</v>
+        <v>4619</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -607,20 +607,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Espanha</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10676</v>
+        <v>9293</v>
       </c>
       <c r="C8" t="n">
-        <v>2039</v>
+        <v>4289</v>
       </c>
       <c r="D8" t="n">
-        <v>12715</v>
+        <v>13582</v>
       </c>
       <c r="E8" t="n">
-        <v>8637</v>
+        <v>5004</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -631,20 +631,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>Itália</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7089</v>
+        <v>7921</v>
       </c>
       <c r="C9" t="n">
-        <v>5419</v>
+        <v>5283</v>
       </c>
       <c r="D9" t="n">
-        <v>12508</v>
+        <v>13204</v>
       </c>
       <c r="E9" t="n">
-        <v>1670</v>
+        <v>2638</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -655,20 +655,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>França</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6017</v>
+        <v>10676</v>
       </c>
       <c r="C10" t="n">
-        <v>3465</v>
+        <v>2039</v>
       </c>
       <c r="D10" t="n">
-        <v>9482</v>
+        <v>12715</v>
       </c>
       <c r="E10" t="n">
-        <v>2552</v>
+        <v>8637</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -679,20 +679,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>Suíça</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7194</v>
+        <v>7089</v>
       </c>
       <c r="C11" t="n">
-        <v>1776</v>
+        <v>5419</v>
       </c>
       <c r="D11" t="n">
-        <v>8970</v>
+        <v>12508</v>
       </c>
       <c r="E11" t="n">
-        <v>5418</v>
+        <v>1670</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -703,20 +703,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Holanda</t>
+          <t>Austrália</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5578</v>
+        <v>6017</v>
       </c>
       <c r="C12" t="n">
-        <v>1383</v>
+        <v>3465</v>
       </c>
       <c r="D12" t="n">
-        <v>6961</v>
+        <v>9482</v>
       </c>
       <c r="E12" t="n">
-        <v>4195</v>
+        <v>2552</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -727,20 +727,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Irlanda</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3064</v>
+        <v>7194</v>
       </c>
       <c r="C13" t="n">
-        <v>2154</v>
+        <v>1776</v>
       </c>
       <c r="D13" t="n">
-        <v>5218</v>
+        <v>8970</v>
       </c>
       <c r="E13" t="n">
-        <v>910</v>
+        <v>5418</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -751,20 +751,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Líbano</t>
+          <t>Holanda</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2736</v>
+        <v>5578</v>
       </c>
       <c r="C14" t="n">
-        <v>1276</v>
+        <v>1383</v>
       </c>
       <c r="D14" t="n">
-        <v>4012</v>
+        <v>6961</v>
       </c>
       <c r="E14" t="n">
-        <v>1460</v>
+        <v>4195</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -775,20 +775,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2127</v>
+        <v>4466</v>
       </c>
       <c r="C15" t="n">
-        <v>591</v>
+        <v>2028</v>
       </c>
       <c r="D15" t="n">
-        <v>2718</v>
+        <v>6494</v>
       </c>
       <c r="E15" t="n">
-        <v>1536</v>
+        <v>2438</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -799,20 +799,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>Paraguai</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1383</v>
+        <v>703</v>
       </c>
       <c r="C16" t="n">
-        <v>243</v>
+        <v>4542</v>
       </c>
       <c r="D16" t="n">
-        <v>1626</v>
+        <v>5245</v>
       </c>
       <c r="E16" t="n">
-        <v>1140</v>
+        <v>-3839</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -823,20 +823,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1178</v>
+        <v>3064</v>
       </c>
       <c r="C17" t="n">
-        <v>393</v>
+        <v>2154</v>
       </c>
       <c r="D17" t="n">
-        <v>1571</v>
+        <v>5218</v>
       </c>
       <c r="E17" t="n">
-        <v>785</v>
+        <v>910</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -847,20 +847,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Emirados Árabes</t>
+          <t>Líbano</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>643</v>
+        <v>2736</v>
       </c>
       <c r="C18" t="n">
-        <v>772</v>
+        <v>1276</v>
       </c>
       <c r="D18" t="n">
-        <v>1415</v>
+        <v>4012</v>
       </c>
       <c r="E18" t="n">
-        <v>-129</v>
+        <v>1460</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -871,20 +871,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Suécia</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>820</v>
+        <v>2127</v>
       </c>
       <c r="C19" t="n">
-        <v>248</v>
+        <v>591</v>
       </c>
       <c r="D19" t="n">
-        <v>1068</v>
+        <v>2718</v>
       </c>
       <c r="E19" t="n">
-        <v>572</v>
+        <v>1536</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -895,20 +895,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Palestina</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>946</v>
       </c>
       <c r="D20" t="n">
-        <v>1046</v>
+        <v>2046</v>
       </c>
       <c r="E20" t="n">
-        <v>954</v>
+        <v>154</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -919,20 +919,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Uruguai</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166</v>
+        <v>887</v>
       </c>
       <c r="C21" t="n">
-        <v>699</v>
+        <v>805</v>
       </c>
       <c r="D21" t="n">
-        <v>865</v>
+        <v>1692</v>
       </c>
       <c r="E21" t="n">
-        <v>-533</v>
+        <v>82</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -943,20 +943,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jordânia</t>
+          <t>Dinamarca</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>725</v>
+        <v>1383</v>
       </c>
       <c r="C22" t="n">
-        <v>76</v>
+        <v>243</v>
       </c>
       <c r="D22" t="n">
-        <v>801</v>
+        <v>1626</v>
       </c>
       <c r="E22" t="n">
-        <v>649</v>
+        <v>1140</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -967,20 +967,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Áustria</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>502</v>
+        <v>1178</v>
       </c>
       <c r="C23" t="n">
-        <v>267</v>
+        <v>393</v>
       </c>
       <c r="D23" t="n">
-        <v>769</v>
+        <v>1571</v>
       </c>
       <c r="E23" t="n">
-        <v>235</v>
+        <v>785</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -991,20 +991,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>Emirados Árabes</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>550</v>
+        <v>643</v>
       </c>
       <c r="C24" t="n">
-        <v>185</v>
+        <v>772</v>
       </c>
       <c r="D24" t="n">
-        <v>735</v>
+        <v>1415</v>
       </c>
       <c r="E24" t="n">
-        <v>365</v>
+        <v>-129</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1015,20 +1015,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>México</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>255</v>
+        <v>699</v>
       </c>
       <c r="C25" t="n">
-        <v>311</v>
+        <v>658</v>
       </c>
       <c r="D25" t="n">
-        <v>566</v>
+        <v>1357</v>
       </c>
       <c r="E25" t="n">
-        <v>-56</v>
+        <v>41</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1039,20 +1039,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nova Zelândia</t>
+          <t>Guiana Francesa</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>418</v>
+        <v>599</v>
       </c>
       <c r="C26" t="n">
-        <v>101</v>
+        <v>563</v>
       </c>
       <c r="D26" t="n">
-        <v>519</v>
+        <v>1162</v>
       </c>
       <c r="E26" t="n">
-        <v>317</v>
+        <v>36</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1063,20 +1063,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>355</v>
+        <v>820</v>
       </c>
       <c r="C27" t="n">
-        <v>117</v>
+        <v>248</v>
       </c>
       <c r="D27" t="n">
-        <v>472</v>
+        <v>1068</v>
       </c>
       <c r="E27" t="n">
-        <v>238</v>
+        <v>572</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1087,20 +1087,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>África do Sul</t>
+          <t>Palestina</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>186</v>
+        <v>1000</v>
       </c>
       <c r="C28" t="n">
-        <v>256</v>
+        <v>46</v>
       </c>
       <c r="D28" t="n">
-        <v>442</v>
+        <v>1046</v>
       </c>
       <c r="E28" t="n">
-        <v>-70</v>
+        <v>954</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1111,20 +1111,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>304</v>
+        <v>166</v>
       </c>
       <c r="C29" t="n">
-        <v>86</v>
+        <v>699</v>
       </c>
       <c r="D29" t="n">
-        <v>390</v>
+        <v>865</v>
       </c>
       <c r="E29" t="n">
-        <v>218</v>
+        <v>-533</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1135,20 +1135,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>Jordânia</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>268</v>
+        <v>725</v>
       </c>
       <c r="C30" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D30" t="n">
-        <v>357</v>
+        <v>801</v>
       </c>
       <c r="E30" t="n">
-        <v>179</v>
+        <v>649</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1159,20 +1159,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Catar</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>159</v>
+        <v>502</v>
       </c>
       <c r="C31" t="n">
-        <v>195</v>
+        <v>267</v>
       </c>
       <c r="D31" t="n">
-        <v>354</v>
+        <v>769</v>
       </c>
       <c r="E31" t="n">
-        <v>-36</v>
+        <v>235</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1183,20 +1183,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Finlândia</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>213</v>
+        <v>550</v>
       </c>
       <c r="C32" t="n">
-        <v>121</v>
+        <v>185</v>
       </c>
       <c r="D32" t="n">
-        <v>334</v>
+        <v>735</v>
       </c>
       <c r="E32" t="n">
-        <v>92</v>
+        <v>365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1207,20 +1207,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>167</v>
+        <v>297</v>
       </c>
       <c r="C33" t="n">
-        <v>118</v>
+        <v>424</v>
       </c>
       <c r="D33" t="n">
-        <v>285</v>
+        <v>721</v>
       </c>
       <c r="E33" t="n">
-        <v>49</v>
+        <v>-127</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1231,20 +1231,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>148</v>
+        <v>267</v>
       </c>
       <c r="C34" t="n">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="D34" t="n">
-        <v>230</v>
+        <v>696</v>
       </c>
       <c r="E34" t="n">
-        <v>66</v>
+        <v>-162</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1255,20 +1255,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Moçambique</t>
+          <t>Grécia</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>108</v>
+        <v>255</v>
       </c>
       <c r="C35" t="n">
-        <v>117</v>
+        <v>311</v>
       </c>
       <c r="D35" t="n">
-        <v>225</v>
+        <v>566</v>
       </c>
       <c r="E35" t="n">
-        <v>-9</v>
+        <v>-56</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1279,20 +1279,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Colômbia</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>94</v>
+        <v>281</v>
       </c>
       <c r="C36" t="n">
-        <v>130</v>
+        <v>283</v>
       </c>
       <c r="D36" t="n">
-        <v>224</v>
+        <v>564</v>
       </c>
       <c r="E36" t="n">
-        <v>-36</v>
+        <v>-2</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1303,20 +1303,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>Suriname</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C37" t="n">
-        <v>33</v>
+        <v>386</v>
       </c>
       <c r="D37" t="n">
-        <v>193</v>
+        <v>558</v>
       </c>
       <c r="E37" t="n">
-        <v>127</v>
+        <v>-214</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1327,20 +1327,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Síria</t>
+          <t>Nova Zelândia</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>106</v>
+        <v>418</v>
       </c>
       <c r="C38" t="n">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="D38" t="n">
-        <v>117</v>
+        <v>519</v>
       </c>
       <c r="E38" t="n">
-        <v>95</v>
+        <v>317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1351,20 +1351,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Tailândia</t>
+          <t>Hungria</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>56</v>
+        <v>355</v>
       </c>
       <c r="C39" t="n">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="D39" t="n">
-        <v>116</v>
+        <v>472</v>
       </c>
       <c r="E39" t="n">
-        <v>-4</v>
+        <v>238</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1375,20 +1375,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>África do Sul</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>67</v>
+        <v>186</v>
       </c>
       <c r="C40" t="n">
-        <v>28</v>
+        <v>256</v>
       </c>
       <c r="D40" t="n">
-        <v>95</v>
+        <v>442</v>
       </c>
       <c r="E40" t="n">
-        <v>39</v>
+        <v>-70</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1399,20 +1399,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Malásia</t>
+          <t>República Tcheca</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>41</v>
+        <v>304</v>
       </c>
       <c r="C41" t="n">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="D41" t="n">
-        <v>85</v>
+        <v>390</v>
       </c>
       <c r="E41" t="n">
-        <v>-3</v>
+        <v>218</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1423,20 +1423,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="C42" t="n">
-        <v>22</v>
+        <v>186</v>
       </c>
       <c r="D42" t="n">
-        <v>81</v>
+        <v>366</v>
       </c>
       <c r="E42" t="n">
-        <v>37</v>
+        <v>-6</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1447,20 +1447,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Arábia Saudita</t>
+          <t>Polônia</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>49</v>
+        <v>268</v>
       </c>
       <c r="C43" t="n">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="D43" t="n">
-        <v>80</v>
+        <v>357</v>
       </c>
       <c r="E43" t="n">
-        <v>18</v>
+        <v>179</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1471,20 +1471,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Catar</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>62</v>
+        <v>159</v>
       </c>
       <c r="C44" t="n">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="D44" t="n">
-        <v>79</v>
+        <v>354</v>
       </c>
       <c r="E44" t="n">
-        <v>45</v>
+        <v>-36</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1495,20 +1495,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Equador</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="C45" t="n">
-        <v>29</v>
+        <v>185</v>
       </c>
       <c r="D45" t="n">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="E45" t="n">
-        <v>19</v>
+        <v>-27</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1519,20 +1519,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Egito</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>60</v>
+        <v>213</v>
       </c>
       <c r="C46" t="n">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="D46" t="n">
-        <v>76</v>
+        <v>334</v>
       </c>
       <c r="E46" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1543,20 +1543,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Filipinas</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="C47" t="n">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="D47" t="n">
-        <v>66</v>
+        <v>285</v>
       </c>
       <c r="E47" t="n">
-        <v>-12</v>
+        <v>49</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1567,20 +1567,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="C48" t="n">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="D48" t="n">
-        <v>65</v>
+        <v>242</v>
       </c>
       <c r="E48" t="n">
-        <v>15</v>
+        <v>-30</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1591,20 +1591,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>Coreia do Sul</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="C49" t="n">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="D49" t="n">
-        <v>61</v>
+        <v>230</v>
       </c>
       <c r="E49" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1615,20 +1615,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>Moçambique</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="C50" t="n">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="D50" t="n">
-        <v>57</v>
+        <v>225</v>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>-9</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1639,20 +1639,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="C51" t="n">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="D51" t="n">
-        <v>54</v>
+        <v>224</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>-36</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1663,20 +1663,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sérvia</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="C52" t="n">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="D52" t="n">
-        <v>48</v>
+        <v>208</v>
       </c>
       <c r="E52" t="n">
-        <v>22</v>
+        <v>-28</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1687,20 +1687,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Quênia</t>
+          <t>Estônia</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29</v>
+        <v>160</v>
       </c>
       <c r="C53" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D53" t="n">
-        <v>45</v>
+        <v>193</v>
       </c>
       <c r="E53" t="n">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1711,20 +1711,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="C54" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D54" t="n">
-        <v>38</v>
+        <v>164</v>
       </c>
       <c r="E54" t="n">
-        <v>-8</v>
+        <v>90</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1735,22 +1735,1102 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>43</v>
+      </c>
+      <c r="C55" t="n">
+        <v>76</v>
+      </c>
+      <c r="D55" t="n">
+        <v>119</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-33</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Síria</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>106</v>
+      </c>
+      <c r="C56" t="n">
+        <v>11</v>
+      </c>
+      <c r="D56" t="n">
+        <v>117</v>
+      </c>
+      <c r="E56" t="n">
+        <v>95</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Tailândia</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="n">
+        <v>60</v>
+      </c>
+      <c r="D57" t="n">
+        <v>116</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Eslovênia</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>67</v>
+      </c>
+      <c r="C58" t="n">
+        <v>28</v>
+      </c>
+      <c r="D58" t="n">
+        <v>95</v>
+      </c>
+      <c r="E58" t="n">
+        <v>39</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Rússia</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>60</v>
+      </c>
+      <c r="C59" t="n">
+        <v>33</v>
+      </c>
+      <c r="D59" t="n">
+        <v>93</v>
+      </c>
+      <c r="E59" t="n">
+        <v>27</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Malásia</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>41</v>
+      </c>
+      <c r="C60" t="n">
+        <v>44</v>
+      </c>
+      <c r="D60" t="n">
+        <v>85</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>59</v>
+      </c>
+      <c r="C61" t="n">
+        <v>22</v>
+      </c>
+      <c r="D61" t="n">
+        <v>81</v>
+      </c>
+      <c r="E61" t="n">
+        <v>37</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Arábia Saudita</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>49</v>
+      </c>
+      <c r="C62" t="n">
+        <v>31</v>
+      </c>
+      <c r="D62" t="n">
+        <v>80</v>
+      </c>
+      <c r="E62" t="n">
+        <v>18</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="n">
+        <v>17</v>
+      </c>
+      <c r="D63" t="n">
+        <v>79</v>
+      </c>
+      <c r="E63" t="n">
+        <v>45</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Cabo Verde</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>48</v>
+      </c>
+      <c r="C64" t="n">
+        <v>29</v>
+      </c>
+      <c r="D64" t="n">
+        <v>77</v>
+      </c>
+      <c r="E64" t="n">
+        <v>19</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Egito</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>60</v>
+      </c>
+      <c r="C65" t="n">
+        <v>16</v>
+      </c>
+      <c r="D65" t="n">
+        <v>76</v>
+      </c>
+      <c r="E65" t="n">
+        <v>44</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>26</v>
+      </c>
+      <c r="C66" t="n">
+        <v>49</v>
+      </c>
+      <c r="D66" t="n">
+        <v>75</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-23</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Nicarágua</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>30</v>
+      </c>
+      <c r="C67" t="n">
+        <v>39</v>
+      </c>
+      <c r="D67" t="n">
+        <v>69</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Filipinas</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>27</v>
+      </c>
+      <c r="C68" t="n">
+        <v>39</v>
+      </c>
+      <c r="D68" t="n">
+        <v>66</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Romênia</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>40</v>
+      </c>
+      <c r="C69" t="n">
+        <v>25</v>
+      </c>
+      <c r="D69" t="n">
+        <v>65</v>
+      </c>
+      <c r="E69" t="n">
+        <v>15</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>20</v>
+      </c>
+      <c r="C70" t="n">
+        <v>44</v>
+      </c>
+      <c r="D70" t="n">
+        <v>64</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-24</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Eslováquia</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>47</v>
+      </c>
+      <c r="C71" t="n">
+        <v>14</v>
+      </c>
+      <c r="D71" t="n">
+        <v>61</v>
+      </c>
+      <c r="E71" t="n">
+        <v>33</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Índia</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>33</v>
+      </c>
+      <c r="C72" t="n">
+        <v>24</v>
+      </c>
+      <c r="D72" t="n">
+        <v>57</v>
+      </c>
+      <c r="E72" t="n">
+        <v>9</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Croácia</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>31</v>
+      </c>
+      <c r="C73" t="n">
+        <v>26</v>
+      </c>
+      <c r="D73" t="n">
+        <v>57</v>
+      </c>
+      <c r="E73" t="n">
+        <v>5</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Guiana</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>8</v>
+      </c>
+      <c r="C74" t="n">
+        <v>47</v>
+      </c>
+      <c r="D74" t="n">
+        <v>55</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-39</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Chipre</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>29</v>
+      </c>
+      <c r="C75" t="n">
+        <v>25</v>
+      </c>
+      <c r="D75" t="n">
+        <v>54</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Bulgária</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>40</v>
+      </c>
+      <c r="C76" t="n">
+        <v>13</v>
+      </c>
+      <c r="D76" t="n">
+        <v>53</v>
+      </c>
+      <c r="E76" t="n">
+        <v>27</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Costa do Marfim</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>31</v>
+      </c>
+      <c r="C77" t="n">
+        <v>22</v>
+      </c>
+      <c r="D77" t="n">
+        <v>53</v>
+      </c>
+      <c r="E77" t="n">
+        <v>9</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Timor-Leste</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>18</v>
+      </c>
+      <c r="C78" t="n">
+        <v>33</v>
+      </c>
+      <c r="D78" t="n">
+        <v>51</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-15</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Sérvia</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>35</v>
+      </c>
+      <c r="C79" t="n">
+        <v>13</v>
+      </c>
+      <c r="D79" t="n">
+        <v>48</v>
+      </c>
+      <c r="E79" t="n">
+        <v>22</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Quênia</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>29</v>
+      </c>
+      <c r="C80" t="n">
+        <v>16</v>
+      </c>
+      <c r="D80" t="n">
+        <v>45</v>
+      </c>
+      <c r="E80" t="n">
+        <v>13</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Cuba</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>43</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>44</v>
+      </c>
+      <c r="E81" t="n">
+        <v>42</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Guiné-Bissau</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>19</v>
+      </c>
+      <c r="C82" t="n">
+        <v>22</v>
+      </c>
+      <c r="D82" t="n">
+        <v>41</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Bahrein</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>11</v>
+      </c>
+      <c r="C83" t="n">
+        <v>28</v>
+      </c>
+      <c r="D83" t="n">
+        <v>39</v>
+      </c>
+      <c r="E83" t="n">
+        <v>-17</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Indonésia</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>15</v>
+      </c>
+      <c r="C84" t="n">
+        <v>23</v>
+      </c>
+      <c r="D84" t="n">
+        <v>38</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Nigéria</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>32</v>
+      </c>
+      <c r="C85" t="n">
+        <v>5</v>
+      </c>
+      <c r="D85" t="n">
+        <v>37</v>
+      </c>
+      <c r="E85" t="n">
+        <v>27</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>Marrocos</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B86" t="n">
         <v>31</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C86" t="n">
         <v>6</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D86" t="n">
         <v>37</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E86" t="n">
         <v>25</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Omã</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>10</v>
+      </c>
+      <c r="C87" t="n">
+        <v>22</v>
+      </c>
+      <c r="D87" t="n">
+        <v>32</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Vietnã</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>15</v>
+      </c>
+      <c r="C88" t="n">
+        <v>17</v>
+      </c>
+      <c r="D88" t="n">
+        <v>32</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Irã</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>11</v>
+      </c>
+      <c r="D89" t="n">
+        <v>27</v>
+      </c>
+      <c r="E89" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Argélia</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>23</v>
+      </c>
+      <c r="C90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D90" t="n">
+        <v>26</v>
+      </c>
+      <c r="E90" t="n">
+        <v>20</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Tunísia</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>7</v>
+      </c>
+      <c r="D91" t="n">
+        <v>23</v>
+      </c>
+      <c r="E91" t="n">
+        <v>9</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Trinidad e Tobago</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>9</v>
+      </c>
+      <c r="C92" t="n">
+        <v>12</v>
+      </c>
+      <c r="D92" t="n">
+        <v>21</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Bahamas</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>6</v>
+      </c>
+      <c r="C93" t="n">
+        <v>14</v>
+      </c>
+      <c r="D93" t="n">
+        <v>20</v>
+      </c>
+      <c r="E93" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Ucrânia</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>3</v>
+      </c>
+      <c r="C94" t="n">
+        <v>16</v>
+      </c>
+      <c r="D94" t="n">
+        <v>19</v>
+      </c>
+      <c r="E94" t="n">
+        <v>-13</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Tanzânia</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>11</v>
+      </c>
+      <c r="C95" t="n">
+        <v>6</v>
+      </c>
+      <c r="D95" t="n">
+        <v>17</v>
+      </c>
+      <c r="E95" t="n">
+        <v>5</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>5</v>
+      </c>
+      <c r="C96" t="n">
+        <v>11</v>
+      </c>
+      <c r="D96" t="n">
+        <v>16</v>
+      </c>
+      <c r="E96" t="n">
+        <v>-6</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="n">
+        <v>12</v>
+      </c>
+      <c r="D97" t="n">
+        <v>13</v>
+      </c>
+      <c r="E97" t="n">
+        <v>-11</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Gana</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>8</v>
+      </c>
+      <c r="C98" t="n">
+        <v>5</v>
+      </c>
+      <c r="D98" t="n">
+        <v>13</v>
+      </c>
+      <c r="E98" t="n">
+        <v>3</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Namíbia</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>8</v>
+      </c>
+      <c r="C99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D99" t="n">
+        <v>12</v>
+      </c>
+      <c r="E99" t="n">
+        <v>4</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>6</v>
+      </c>
+      <c r="C100" t="n">
+        <v>2</v>
+      </c>
+      <c r="D100" t="n">
+        <v>8</v>
+      </c>
+      <c r="E100" t="n">
+        <v>4</v>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>https://g1.globo.com/mundo/noticia/2026/10/25/votacao-no-exterior-confira-os-resultados-do-2o-turno-entre-lula-e-flavio-bolsonaro.ghtml</t>
         </is>
